--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/119.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/119.xlsx
@@ -426,13 +426,13 @@
         <v>-9.673196243466878</v>
       </c>
       <c r="E2">
-        <v>-27.66987942990101</v>
+        <v>-26.54355737471324</v>
       </c>
       <c r="F2">
-        <v>-3.609998780890864</v>
+        <v>-4.221543501109807</v>
       </c>
       <c r="G2">
-        <v>-15.95382632987857</v>
+        <v>-14.07535823525808</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.654810331940636</v>
       </c>
       <c r="E3">
-        <v>-28.09987162235134</v>
+        <v>-25.19663523671582</v>
       </c>
       <c r="F3">
-        <v>-3.628212094976216</v>
+        <v>-3.497402113297938</v>
       </c>
       <c r="G3">
-        <v>-16.36876845249805</v>
+        <v>-12.96780529345829</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.592580384590638</v>
       </c>
       <c r="E4">
-        <v>-28.74599882223975</v>
+        <v>-26.7810486655715</v>
       </c>
       <c r="F4">
-        <v>-3.464361851069877</v>
+        <v>-3.748928419851383</v>
       </c>
       <c r="G4">
-        <v>-15.67698858024809</v>
+        <v>-13.24181583719822</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.488120014684524</v>
       </c>
       <c r="E5">
-        <v>-28.71577125823855</v>
+        <v>-27.60803858885227</v>
       </c>
       <c r="F5">
-        <v>-3.582951756822057</v>
+        <v>-4.002491681848311</v>
       </c>
       <c r="G5">
-        <v>-15.92417211821055</v>
+        <v>-13.1886120598366</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.334582068955564</v>
       </c>
       <c r="E6">
-        <v>-28.93127680778958</v>
+        <v>-27.22490704543332</v>
       </c>
       <c r="F6">
-        <v>-3.545169919580371</v>
+        <v>-3.940478441339935</v>
       </c>
       <c r="G6">
-        <v>-16.19841771068377</v>
+        <v>-13.49760679356278</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.128285163074336</v>
       </c>
       <c r="E7">
-        <v>-29.00577926216377</v>
+        <v>-29.02499810585232</v>
       </c>
       <c r="F7">
-        <v>-3.551057126712068</v>
+        <v>-3.955868679316547</v>
       </c>
       <c r="G7">
-        <v>-15.75686045720132</v>
+        <v>-13.6272609990628</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.85732793047158</v>
       </c>
       <c r="E8">
-        <v>-28.76493690053983</v>
+        <v>-29.04579285849554</v>
       </c>
       <c r="F8">
-        <v>-3.505250894439463</v>
+        <v>-3.890862547381856</v>
       </c>
       <c r="G8">
-        <v>-15.65440238330642</v>
+        <v>-13.64224783871908</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.509841897814043</v>
       </c>
       <c r="E9">
-        <v>-29.74420581927652</v>
+        <v>-28.64721469023643</v>
       </c>
       <c r="F9">
-        <v>-3.625726992767818</v>
+        <v>-3.95855341806902</v>
       </c>
       <c r="G9">
-        <v>-15.46548775738067</v>
+        <v>-13.78236336812319</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.084032284619493</v>
       </c>
       <c r="E10">
-        <v>-30.29288252275687</v>
+        <v>-29.40105617287129</v>
       </c>
       <c r="F10">
-        <v>-3.662470885653796</v>
+        <v>-3.871231896670313</v>
       </c>
       <c r="G10">
-        <v>-15.43479403441332</v>
+        <v>-12.55626144583487</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.580931908031268</v>
       </c>
       <c r="E11">
-        <v>-31.2581199647808</v>
+        <v>-30.89818552946614</v>
       </c>
       <c r="F11">
-        <v>-3.596765611631142</v>
+        <v>-3.942597405156296</v>
       </c>
       <c r="G11">
-        <v>-14.84764891975034</v>
+        <v>-12.53453102491509</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.011169092918992</v>
       </c>
       <c r="E12">
-        <v>-31.45459233807758</v>
+        <v>-31.03562697983594</v>
       </c>
       <c r="F12">
-        <v>-3.517319379130849</v>
+        <v>-4.361148259503608</v>
       </c>
       <c r="G12">
-        <v>-14.41698998218317</v>
+        <v>-11.49243418951777</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.390443949143298</v>
       </c>
       <c r="E13">
-        <v>-31.6836697242296</v>
+        <v>-31.20438509220578</v>
       </c>
       <c r="F13">
-        <v>-3.637769798069717</v>
+        <v>-4.03728891133771</v>
       </c>
       <c r="G13">
-        <v>-14.65163979473394</v>
+        <v>-11.60660166298507</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.754162869838356</v>
       </c>
       <c r="E14">
-        <v>-32.18866929590597</v>
+        <v>-32.3644488072247</v>
       </c>
       <c r="F14">
-        <v>-3.569517294283455</v>
+        <v>-3.923024740162949</v>
       </c>
       <c r="G14">
-        <v>-14.02834517805489</v>
+        <v>-11.98007754745241</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.131954137434829</v>
       </c>
       <c r="E15">
-        <v>-33.72108905044259</v>
+        <v>-33.58408459781453</v>
       </c>
       <c r="F15">
-        <v>-3.526288941368362</v>
+        <v>-3.879099730262102</v>
       </c>
       <c r="G15">
-        <v>-13.6843530121603</v>
+        <v>-11.44025337072778</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.552165503592476</v>
       </c>
       <c r="E16">
-        <v>-33.57667601433798</v>
+        <v>-34.51436222049924</v>
       </c>
       <c r="F16">
-        <v>-3.094258892642697</v>
+        <v>-3.386947603808652</v>
       </c>
       <c r="G16">
-        <v>-13.57359043478013</v>
+        <v>-10.68272771934066</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.040961687192095</v>
       </c>
       <c r="E17">
-        <v>-34.13776752931036</v>
+        <v>-35.22391069886508</v>
       </c>
       <c r="F17">
-        <v>-3.433107548962252</v>
+        <v>-3.815183729829496</v>
       </c>
       <c r="G17">
-        <v>-13.35072947489471</v>
+        <v>-9.95955228846903</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.616912589866159</v>
       </c>
       <c r="E18">
-        <v>-35.84233043053756</v>
+        <v>-34.92633335063604</v>
       </c>
       <c r="F18">
-        <v>-3.029377844185829</v>
+        <v>-3.461653089662723</v>
       </c>
       <c r="G18">
-        <v>-13.00579380352142</v>
+        <v>-10.22643522766292</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.285694734099127</v>
       </c>
       <c r="E19">
-        <v>-35.78958050105921</v>
+        <v>-35.29084607317245</v>
       </c>
       <c r="F19">
-        <v>-2.816212403688626</v>
+        <v>-3.541679179344974</v>
       </c>
       <c r="G19">
-        <v>-12.59813984690665</v>
+        <v>-8.606449562930413</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.041968345539483</v>
       </c>
       <c r="E20">
-        <v>-36.531573231453</v>
+        <v>-36.08701293812</v>
       </c>
       <c r="F20">
-        <v>-2.956892382971261</v>
+        <v>-3.091625512669197</v>
       </c>
       <c r="G20">
-        <v>-12.38861210918063</v>
+        <v>-9.136302376490768</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.881537871522871</v>
       </c>
       <c r="E21">
-        <v>-37.09996464652575</v>
+        <v>-37.74972368256832</v>
       </c>
       <c r="F21">
-        <v>-2.571085235321808</v>
+        <v>-2.812280143627537</v>
       </c>
       <c r="G21">
-        <v>-12.18522212288443</v>
+        <v>-8.895344319414914</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.788439122437674</v>
       </c>
       <c r="E22">
-        <v>-37.5023422044773</v>
+        <v>-37.69419553428626</v>
       </c>
       <c r="F22">
-        <v>-2.624765928125424</v>
+        <v>-2.986777393762059</v>
       </c>
       <c r="G22">
-        <v>-11.94020864752297</v>
+        <v>-9.247861140073129</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.744350949959025</v>
       </c>
       <c r="E23">
-        <v>-37.92566169047732</v>
+        <v>-37.91280761700655</v>
       </c>
       <c r="F23">
-        <v>-2.385376032390395</v>
+        <v>-2.95837764572448</v>
       </c>
       <c r="G23">
-        <v>-11.95373553659643</v>
+        <v>-9.212438302802926</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.729657439338153</v>
       </c>
       <c r="E24">
-        <v>-38.29305678671962</v>
+        <v>-38.45740869388</v>
       </c>
       <c r="F24">
-        <v>-2.427727972593325</v>
+        <v>-2.883291939232524</v>
       </c>
       <c r="G24">
-        <v>-12.3558840559794</v>
+        <v>-8.177111533033411</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.730226384192819</v>
       </c>
       <c r="E25">
-        <v>-38.59012694585979</v>
+        <v>-38.21533685156297</v>
       </c>
       <c r="F25">
-        <v>-2.134034451767775</v>
+        <v>-2.643913640641135</v>
       </c>
       <c r="G25">
-        <v>-12.64983401550237</v>
+        <v>-8.622591782979899</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.730887477505408</v>
       </c>
       <c r="E26">
-        <v>-39.0172707281593</v>
+        <v>-38.65726157302351</v>
       </c>
       <c r="F26">
-        <v>-2.113897668573121</v>
+        <v>-2.754726833215833</v>
       </c>
       <c r="G26">
-        <v>-12.09475484493277</v>
+        <v>-8.781514521592614</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.721932743058349</v>
       </c>
       <c r="E27">
-        <v>-38.5992223859042</v>
+        <v>-38.67308858968032</v>
       </c>
       <c r="F27">
-        <v>-2.097883669942201</v>
+        <v>-2.688908072858995</v>
       </c>
       <c r="G27">
-        <v>-12.45822957132597</v>
+        <v>-9.849993094392389</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.701528593491958</v>
       </c>
       <c r="E28">
-        <v>-38.6984072878572</v>
+        <v>-38.861824065135</v>
       </c>
       <c r="F28">
-        <v>-2.120519637591101</v>
+        <v>-2.419916467984926</v>
       </c>
       <c r="G28">
-        <v>-12.35967132007633</v>
+        <v>-9.583742469396503</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.669366569987486</v>
       </c>
       <c r="E29">
-        <v>-39.56702067997946</v>
+        <v>-38.82499625026762</v>
       </c>
       <c r="F29">
-        <v>-2.044585682878678</v>
+        <v>-2.186824649613381</v>
       </c>
       <c r="G29">
-        <v>-12.72455633886926</v>
+        <v>-9.388109091298812</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.630472409502309</v>
       </c>
       <c r="E30">
-        <v>-38.42704980413257</v>
+        <v>-39.49521946035085</v>
       </c>
       <c r="F30">
-        <v>-1.966715005178511</v>
+        <v>-2.639561398306826</v>
       </c>
       <c r="G30">
-        <v>-12.66483078679527</v>
+        <v>-9.498280736300218</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.591013661002582</v>
       </c>
       <c r="E31">
-        <v>-38.33543198224639</v>
+        <v>-38.71806086505049</v>
       </c>
       <c r="F31">
-        <v>-1.764468275417609</v>
+        <v>-2.425220504465051</v>
       </c>
       <c r="G31">
-        <v>-12.64937053912687</v>
+        <v>-9.973387058277645</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.560862676458576</v>
       </c>
       <c r="E32">
-        <v>-37.76401554653652</v>
+        <v>-37.1961675483447</v>
       </c>
       <c r="F32">
-        <v>-1.970678743200906</v>
+        <v>-2.425245355487135</v>
       </c>
       <c r="G32">
-        <v>-12.37077488981504</v>
+        <v>-9.843352140040611</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.545081366233983</v>
       </c>
       <c r="E33">
-        <v>-38.06334314996953</v>
+        <v>-37.63578954077234</v>
       </c>
       <c r="F33">
-        <v>-1.991469936643771</v>
+        <v>-2.73892489664003</v>
       </c>
       <c r="G33">
-        <v>-13.20055981868783</v>
+        <v>-10.00285091357716</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.549387860400838</v>
       </c>
       <c r="E34">
-        <v>-37.24670758250731</v>
+        <v>-36.73580288072493</v>
       </c>
       <c r="F34">
-        <v>-2.089152677516695</v>
+        <v>-2.915366325068921</v>
       </c>
       <c r="G34">
-        <v>-13.08087697635209</v>
+        <v>-9.784308560347709</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.576589802921959</v>
       </c>
       <c r="E35">
-        <v>-36.98414439530557</v>
+        <v>-36.5717747594561</v>
       </c>
       <c r="F35">
-        <v>-1.803463670904395</v>
+        <v>-2.571525098412694</v>
       </c>
       <c r="G35">
-        <v>-13.1887047551117</v>
+        <v>-9.99194266602526</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.626120781560922</v>
       </c>
       <c r="E36">
-        <v>-36.69848372642772</v>
+        <v>-36.59756215469277</v>
       </c>
       <c r="F36">
-        <v>-1.841779805120886</v>
+        <v>-2.036027819240357</v>
       </c>
       <c r="G36">
-        <v>-13.20100343179009</v>
+        <v>-10.55623839537619</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.696956272453043</v>
       </c>
       <c r="E37">
-        <v>-36.42232153178095</v>
+        <v>-35.73999597491223</v>
       </c>
       <c r="F37">
-        <v>-1.998619575697334</v>
+        <v>-2.393265403534657</v>
       </c>
       <c r="G37">
-        <v>-13.15129890106347</v>
+        <v>-10.20334086198096</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.787419399041849</v>
       </c>
       <c r="E38">
-        <v>-35.53984421648421</v>
+        <v>-34.61599476265339</v>
       </c>
       <c r="F38">
-        <v>-1.989496765490303</v>
+        <v>-2.626515440080137</v>
       </c>
       <c r="G38">
-        <v>-13.60150495476727</v>
+        <v>-11.04224965435997</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.897643978454725</v>
       </c>
       <c r="E39">
-        <v>-34.56807671494122</v>
+        <v>-33.57766322167166</v>
       </c>
       <c r="F39">
-        <v>-1.84614530133364</v>
+        <v>-2.005963881090554</v>
       </c>
       <c r="G39">
-        <v>-13.70930459388979</v>
+        <v>-11.01249778159855</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.022956986975963</v>
       </c>
       <c r="E40">
-        <v>-34.65039531545266</v>
+        <v>-32.74674937566325</v>
       </c>
       <c r="F40">
-        <v>-1.702885785958688</v>
+        <v>-2.15567803526812</v>
       </c>
       <c r="G40">
-        <v>-13.75433463431495</v>
+        <v>-10.87882457381385</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.16482165221713</v>
       </c>
       <c r="E41">
-        <v>-34.72482078576871</v>
+        <v>-32.73879511106878</v>
       </c>
       <c r="F41">
-        <v>-1.729854943491631</v>
+        <v>-2.173101915218605</v>
       </c>
       <c r="G41">
-        <v>-13.12694321753105</v>
+        <v>-11.19890135873275</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.323689842743398</v>
       </c>
       <c r="E42">
-        <v>-33.78871954551014</v>
+        <v>-33.38020137680419</v>
       </c>
       <c r="F42">
-        <v>-1.750518568354465</v>
+        <v>-2.478007388841047</v>
       </c>
       <c r="G42">
-        <v>-13.97780970039791</v>
+        <v>-10.71305893757147</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.500915415298742</v>
       </c>
       <c r="E43">
-        <v>-33.43096330619317</v>
+        <v>-32.25972784579733</v>
       </c>
       <c r="F43">
-        <v>-1.723783838796514</v>
+        <v>-2.101131698528578</v>
       </c>
       <c r="G43">
-        <v>-13.52918112164358</v>
+        <v>-11.24493780500185</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.697304495015164</v>
       </c>
       <c r="E44">
-        <v>-32.37857538189163</v>
+        <v>-31.38956345132744</v>
       </c>
       <c r="F44">
-        <v>-1.445993315369908</v>
+        <v>-2.01304642238449</v>
       </c>
       <c r="G44">
-        <v>-13.60336879190588</v>
+        <v>-10.86692647314571</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.919301147963083</v>
       </c>
       <c r="E45">
-        <v>-32.40895691400909</v>
+        <v>-29.55951653534769</v>
       </c>
       <c r="F45">
-        <v>-1.417492506509188</v>
+        <v>-2.025896057536716</v>
       </c>
       <c r="G45">
-        <v>-13.82503298957886</v>
+        <v>-10.32154720100618</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.174355786754043</v>
       </c>
       <c r="E46">
-        <v>-31.18391638969111</v>
+        <v>-30.54299240643751</v>
       </c>
       <c r="F46">
-        <v>-1.409666919654941</v>
+        <v>-1.867918938516225</v>
       </c>
       <c r="G46">
-        <v>-13.70012445110939</v>
+        <v>-10.7056267628358</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.46251996535142</v>
       </c>
       <c r="E47">
-        <v>-31.1729303117485</v>
+        <v>-29.54550090829395</v>
       </c>
       <c r="F47">
-        <v>-1.434448358877091</v>
+        <v>-1.595912076295965</v>
       </c>
       <c r="G47">
-        <v>-13.61640240969399</v>
+        <v>-11.10621270472423</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.791504151303066</v>
       </c>
       <c r="E48">
-        <v>-29.72859164089807</v>
+        <v>-29.14806844395878</v>
       </c>
       <c r="F48">
-        <v>-1.136666016551322</v>
+        <v>-1.054424872433984</v>
       </c>
       <c r="G48">
-        <v>-13.74757615559653</v>
+        <v>-10.59232334175425</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.166280705307067</v>
       </c>
       <c r="E49">
-        <v>-30.17854987524822</v>
+        <v>-28.63284131373608</v>
       </c>
       <c r="F49">
-        <v>-1.075385881194423</v>
+        <v>-1.549329663766938</v>
       </c>
       <c r="G49">
-        <v>-13.32819790195443</v>
+        <v>-10.38116350507737</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.590063016802272</v>
       </c>
       <c r="E50">
-        <v>-28.81072430123138</v>
+        <v>-27.12192048955088</v>
       </c>
       <c r="F50">
-        <v>-1.324980434964539</v>
+        <v>-1.83661741946664</v>
       </c>
       <c r="G50">
-        <v>-13.66862461030322</v>
+        <v>-10.60930975091625</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.05714948551448</v>
       </c>
       <c r="E51">
-        <v>-28.91494713051792</v>
+        <v>-26.27973300750037</v>
       </c>
       <c r="F51">
-        <v>-0.9644343512634573</v>
+        <v>-1.13824239971885</v>
       </c>
       <c r="G51">
-        <v>-13.36458410797656</v>
+        <v>-10.28771342559483</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.56883920661887</v>
       </c>
       <c r="E52">
-        <v>-28.71052275686366</v>
+        <v>-25.87836982772654</v>
       </c>
       <c r="F52">
-        <v>-1.071038609064531</v>
+        <v>-1.466270921023037</v>
       </c>
       <c r="G52">
-        <v>-13.13185937765687</v>
+        <v>-11.86754548348151</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.120840248695719</v>
       </c>
       <c r="E53">
-        <v>-28.49772070629522</v>
+        <v>-26.00678829363606</v>
       </c>
       <c r="F53">
-        <v>-1.251712166554326</v>
+        <v>-1.375772610634594</v>
       </c>
       <c r="G53">
-        <v>-13.30667604540362</v>
+        <v>-11.73394179715314</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.700157138915244</v>
       </c>
       <c r="E54">
-        <v>-27.39342514868075</v>
+        <v>-24.94196744394646</v>
       </c>
       <c r="F54">
-        <v>-1.164057641459693</v>
+        <v>-1.427746866588443</v>
       </c>
       <c r="G54">
-        <v>-13.52394714914599</v>
+        <v>-11.20597599455017</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.29457910609422</v>
       </c>
       <c r="E55">
-        <v>-27.10631083964644</v>
+        <v>-25.93238999416404</v>
       </c>
       <c r="F55">
-        <v>-1.371898336291701</v>
+        <v>-1.585395952117425</v>
       </c>
       <c r="G55">
-        <v>-13.48680613874091</v>
+        <v>-11.15913508571502</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.891281177643027</v>
       </c>
       <c r="E56">
-        <v>-26.87637757190697</v>
+        <v>-24.90324446270687</v>
       </c>
       <c r="F56">
-        <v>-1.333684919633157</v>
+        <v>-1.452358490493019</v>
       </c>
       <c r="G56">
-        <v>-13.29904854848114</v>
+        <v>-11.40224830793694</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.475969834890194</v>
       </c>
       <c r="E57">
-        <v>-26.02104845828621</v>
+        <v>-23.32376707051954</v>
       </c>
       <c r="F57">
-        <v>-1.12984192588706</v>
+        <v>-1.116940103588458</v>
       </c>
       <c r="G57">
-        <v>-13.3411355139219</v>
+        <v>-11.370092979114</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.02272182497633</v>
       </c>
       <c r="E58">
-        <v>-25.81839924644297</v>
+        <v>-23.9750612592507</v>
       </c>
       <c r="F58">
-        <v>-1.21905212496415</v>
+        <v>-1.94211083658056</v>
       </c>
       <c r="G58">
-        <v>-13.4012748841883</v>
+        <v>-11.8886535218399</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.51716969265292</v>
       </c>
       <c r="E59">
-        <v>-25.42453521962583</v>
+        <v>-23.30434897397465</v>
       </c>
       <c r="F59">
-        <v>-1.176156775744983</v>
+        <v>-1.625779691371304</v>
       </c>
       <c r="G59">
-        <v>-13.2575442390553</v>
+        <v>-11.89148072773044</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.94007941584308</v>
       </c>
       <c r="E60">
-        <v>-25.60020378333138</v>
+        <v>-23.02321225063046</v>
       </c>
       <c r="F60">
-        <v>-1.370325266593784</v>
+        <v>-1.293461883655421</v>
       </c>
       <c r="G60">
-        <v>-13.64344129038598</v>
+        <v>-11.45799458427273</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.27591131130577</v>
       </c>
       <c r="E61">
-        <v>-24.42104349342211</v>
+        <v>-22.03116850671813</v>
       </c>
       <c r="F61">
-        <v>-1.325073212113653</v>
+        <v>-1.753402943651013</v>
       </c>
       <c r="G61">
-        <v>-13.44193500450163</v>
+        <v>-11.20931302445376</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.5092678345427</v>
       </c>
       <c r="E62">
-        <v>-24.82906352998722</v>
+        <v>-23.0181041319498</v>
       </c>
       <c r="F62">
-        <v>-1.674949923666677</v>
+        <v>-2.056645055528633</v>
       </c>
       <c r="G62">
-        <v>-13.07775513190856</v>
+        <v>-11.84212380428544</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.63418730370639</v>
       </c>
       <c r="E63">
-        <v>-24.85711289799073</v>
+        <v>-22.06913523279844</v>
       </c>
       <c r="F63">
-        <v>-1.499629276333773</v>
+        <v>-2.236981467485489</v>
       </c>
       <c r="G63">
-        <v>-13.94756455635113</v>
+        <v>-11.0732827082451</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.65073928699772</v>
       </c>
       <c r="E64">
-        <v>-25.0183854428259</v>
+        <v>-20.39710941731635</v>
       </c>
       <c r="F64">
-        <v>-1.693838357185312</v>
+        <v>-2.064492179935353</v>
       </c>
       <c r="G64">
-        <v>-13.78902253047544</v>
+        <v>-11.73173697382398</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.55893836676336</v>
       </c>
       <c r="E65">
-        <v>-24.52461875092555</v>
+        <v>-21.99344178976023</v>
       </c>
       <c r="F65">
-        <v>-1.927582100702859</v>
+        <v>-2.516885984524039</v>
       </c>
       <c r="G65">
-        <v>-14.00618107566947</v>
+        <v>-12.44921826636807</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.36801103126981</v>
       </c>
       <c r="E66">
-        <v>-24.32709124318498</v>
+        <v>-21.06083426719857</v>
       </c>
       <c r="F66">
-        <v>-1.839726282329347</v>
+        <v>-2.572254061727158</v>
       </c>
       <c r="G66">
-        <v>-13.91213013217154</v>
+        <v>-12.20136765347946</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.08634886799429</v>
       </c>
       <c r="E67">
-        <v>-24.05491184142796</v>
+        <v>-21.6250821285543</v>
       </c>
       <c r="F67">
-        <v>-1.920784517795487</v>
+        <v>-2.660251530926549</v>
       </c>
       <c r="G67">
-        <v>-13.884750265289</v>
+        <v>-11.60868068558374</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.73373875920547</v>
       </c>
       <c r="E68">
-        <v>-24.09211778387498</v>
+        <v>-20.82543965980586</v>
       </c>
       <c r="F68">
-        <v>-2.116461465684786</v>
+        <v>-2.544208854937978</v>
       </c>
       <c r="G68">
-        <v>-13.6811964069886</v>
+        <v>-12.10090252799919</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.32207326363416</v>
       </c>
       <c r="E69">
-        <v>-24.31868639542674</v>
+        <v>-21.6521261753281</v>
       </c>
       <c r="F69">
-        <v>-2.420005103297025</v>
+        <v>-2.7361051340009</v>
       </c>
       <c r="G69">
-        <v>-13.55859366348724</v>
+        <v>-11.3646305789742</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.867060357908473</v>
       </c>
       <c r="E70">
-        <v>-23.78095274938592</v>
+        <v>-20.24483947880843</v>
       </c>
       <c r="F70">
-        <v>-2.494982293659214</v>
+        <v>-2.926743951346372</v>
       </c>
       <c r="G70">
-        <v>-13.69352653384962</v>
+        <v>-10.97299635222396</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.384049971259561</v>
       </c>
       <c r="E71">
-        <v>-23.50033680055261</v>
+        <v>-20.22576101781412</v>
       </c>
       <c r="F71">
-        <v>-2.38000406978324</v>
+        <v>-2.917673328285718</v>
       </c>
       <c r="G71">
-        <v>-13.31097975460468</v>
+        <v>-11.13015457006424</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.891662692010538</v>
       </c>
       <c r="E72">
-        <v>-23.60145309666989</v>
+        <v>-20.98080707453502</v>
       </c>
       <c r="F72">
-        <v>-2.605798799703524</v>
+        <v>-3.295705419492495</v>
       </c>
       <c r="G72">
-        <v>-13.5719186092828</v>
+        <v>-10.68564099941522</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.403402652617546</v>
       </c>
       <c r="E73">
-        <v>-23.64013985011741</v>
+        <v>-20.31126313555294</v>
       </c>
       <c r="F73">
-        <v>-2.645190983176251</v>
+        <v>-3.129771831568115</v>
       </c>
       <c r="G73">
-        <v>-13.47783787087502</v>
+        <v>-11.32018319456395</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.928874514766651</v>
       </c>
       <c r="E74">
-        <v>-24.10040941978302</v>
+        <v>-20.55433350638866</v>
       </c>
       <c r="F74">
-        <v>-2.704924556592124</v>
+        <v>-3.060106132992676</v>
       </c>
       <c r="G74">
-        <v>-13.56710011025039</v>
+        <v>-11.35806245662429</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.484456401331765</v>
       </c>
       <c r="E75">
-        <v>-24.36262617872316</v>
+        <v>-21.60546930762708</v>
       </c>
       <c r="F75">
-        <v>-2.650374078015568</v>
+        <v>-3.607817689519293</v>
       </c>
       <c r="G75">
-        <v>-13.02930198739579</v>
+        <v>-10.49827405352909</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.075195100181773</v>
       </c>
       <c r="E76">
-        <v>-23.88414308659871</v>
+        <v>-21.05599785695838</v>
       </c>
       <c r="F76">
-        <v>-2.87290172689921</v>
+        <v>-3.474932647497001</v>
       </c>
       <c r="G76">
-        <v>-13.23372155335471</v>
+        <v>-10.75660916414058</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.70665909542467</v>
       </c>
       <c r="E77">
-        <v>-24.44290696593115</v>
+        <v>-21.67799281885992</v>
       </c>
       <c r="F77">
-        <v>-3.061169756737871</v>
+        <v>-3.48581242496537</v>
       </c>
       <c r="G77">
-        <v>-12.82104549915685</v>
+        <v>-9.989433272506492</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.378438418604794</v>
       </c>
       <c r="E78">
-        <v>-24.33550967636524</v>
+        <v>-20.82881790141558</v>
       </c>
       <c r="F78">
-        <v>-2.95802558957829</v>
+        <v>-3.829154146077709</v>
       </c>
       <c r="G78">
-        <v>-12.82725277204299</v>
+        <v>-10.79042969736977</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.098465971631385</v>
       </c>
       <c r="E79">
-        <v>-24.99245992913198</v>
+        <v>-20.75047077260887</v>
       </c>
       <c r="F79">
-        <v>-3.055741465147326</v>
+        <v>-3.929237495683946</v>
       </c>
       <c r="G79">
-        <v>-12.25173760385947</v>
+        <v>-9.941953428382265</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.863188251155841</v>
       </c>
       <c r="E80">
-        <v>-25.10037799320877</v>
+        <v>-22.13675893515498</v>
       </c>
       <c r="F80">
-        <v>-3.111165042966432</v>
+        <v>-4.211141691632854</v>
       </c>
       <c r="G80">
-        <v>-12.72773446258696</v>
+        <v>-9.833314565965541</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.670912538517181</v>
       </c>
       <c r="E81">
-        <v>-25.21461327852627</v>
+        <v>-22.50395477854094</v>
       </c>
       <c r="F81">
-        <v>-3.582625380065354</v>
+        <v>-3.537389892933279</v>
       </c>
       <c r="G81">
-        <v>-11.81759597238498</v>
+        <v>-10.1708975156961</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.525011186522408</v>
       </c>
       <c r="E82">
-        <v>-25.7165810368545</v>
+        <v>-23.4404613172232</v>
       </c>
       <c r="F82">
-        <v>-3.175245888512196</v>
+        <v>-3.241049738255783</v>
       </c>
       <c r="G82">
-        <v>-12.28541247308493</v>
+        <v>-9.344297331632097</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.425637074545659</v>
       </c>
       <c r="E83">
-        <v>-26.46476645545378</v>
+        <v>-23.06359265335686</v>
       </c>
       <c r="F83">
-        <v>-3.309588857163415</v>
+        <v>-4.24061500382446</v>
       </c>
       <c r="G83">
-        <v>-12.05055244089242</v>
+        <v>-9.816986955365856</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.375404530791046</v>
       </c>
       <c r="E84">
-        <v>-27.22057329580797</v>
+        <v>-23.54275501658246</v>
       </c>
       <c r="F84">
-        <v>-3.663527054092365</v>
+        <v>-3.962647209773655</v>
       </c>
       <c r="G84">
-        <v>-11.75890331051924</v>
+        <v>-8.551838803714597</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.375304240844996</v>
       </c>
       <c r="E85">
-        <v>-27.14473947007553</v>
+        <v>-25.37531976411047</v>
       </c>
       <c r="F85">
-        <v>-3.382239991858542</v>
+        <v>-4.3123226280478</v>
       </c>
       <c r="G85">
-        <v>-12.26599612349711</v>
+        <v>-8.715601559905725</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.433361025798146</v>
       </c>
       <c r="E86">
-        <v>-28.23698928682959</v>
+        <v>-26.40110969632796</v>
       </c>
       <c r="F86">
-        <v>-3.868607628738244</v>
+        <v>-4.252274275018863</v>
       </c>
       <c r="G86">
-        <v>-11.98432166683376</v>
+        <v>-9.168725859502389</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.546844489077493</v>
       </c>
       <c r="E87">
-        <v>-29.10171045554226</v>
+        <v>-26.99875958196426</v>
       </c>
       <c r="F87">
-        <v>-3.832584415492702</v>
+        <v>-4.349154327878474</v>
       </c>
       <c r="G87">
-        <v>-11.76761004528753</v>
+        <v>-8.494685545524618</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.720016831982586</v>
       </c>
       <c r="E88">
-        <v>-29.2635037748883</v>
+        <v>-27.23459345133572</v>
       </c>
       <c r="F88">
-        <v>-3.907367767882636</v>
+        <v>-4.309593985822977</v>
       </c>
       <c r="G88">
-        <v>-11.90094557742721</v>
+        <v>-9.261268849507177</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.954211348316044</v>
       </c>
       <c r="E89">
-        <v>-30.80198036341018</v>
+        <v>-28.27308575314473</v>
       </c>
       <c r="F89">
-        <v>-4.094323663755262</v>
+        <v>-4.474864879825118</v>
       </c>
       <c r="G89">
-        <v>-12.16039965243097</v>
+        <v>-8.790499342186195</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.247914505394702</v>
       </c>
       <c r="E90">
-        <v>-31.22695500666001</v>
+        <v>-28.89660228231284</v>
       </c>
       <c r="F90">
-        <v>-4.023530557144613</v>
+        <v>-4.476132281951402</v>
       </c>
       <c r="G90">
-        <v>-11.92954206979544</v>
+        <v>-8.627233167825958</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.596483108819198</v>
       </c>
       <c r="E91">
-        <v>-32.56505341305349</v>
+        <v>-30.74913533597768</v>
       </c>
       <c r="F91">
-        <v>-4.458030797465427</v>
+        <v>-4.689199975095073</v>
       </c>
       <c r="G91">
-        <v>-11.89078220262165</v>
+        <v>-9.412775966111923</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.995855297406623</v>
       </c>
       <c r="E92">
-        <v>-34.46679739375968</v>
+        <v>-32.49886297272037</v>
       </c>
       <c r="F92">
-        <v>-4.347198552440464</v>
+        <v>-4.763260991109767</v>
       </c>
       <c r="G92">
-        <v>-11.82262800160468</v>
+        <v>-8.907503953180656</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.441696639478697</v>
       </c>
       <c r="E93">
-        <v>-35.28385184506761</v>
+        <v>-33.49453628854985</v>
       </c>
       <c r="F93">
-        <v>-4.389878526134903</v>
+        <v>-5.173534798368305</v>
       </c>
       <c r="G93">
-        <v>-12.1986993537748</v>
+        <v>-8.986225415558987</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.915305607278575</v>
       </c>
       <c r="E94">
-        <v>-36.50331781788215</v>
+        <v>-34.99825457482586</v>
       </c>
       <c r="F94">
-        <v>-4.488332477059832</v>
+        <v>-5.514689629537254</v>
       </c>
       <c r="G94">
-        <v>-12.76375319805423</v>
+        <v>-10.03773744247</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.40717249110623</v>
       </c>
       <c r="E95">
-        <v>-38.45034427442803</v>
+        <v>-35.46065705574908</v>
       </c>
       <c r="F95">
-        <v>-4.713651724090909</v>
+        <v>-5.139569249751317</v>
       </c>
       <c r="G95">
-        <v>-12.49859836363184</v>
+        <v>-9.678437314001817</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.89797477799625</v>
       </c>
       <c r="E96">
-        <v>-39.2056643038264</v>
+        <v>-37.05716603867926</v>
       </c>
       <c r="F96">
-        <v>-4.647693798010401</v>
+        <v>-5.278622315454854</v>
       </c>
       <c r="G96">
-        <v>-13.24052803498345</v>
+        <v>-10.39238294390996</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.370053549118818</v>
       </c>
       <c r="E97">
-        <v>-40.91133668118547</v>
+        <v>-39.45350315779218</v>
       </c>
       <c r="F97">
-        <v>-4.768381958393872</v>
+        <v>-5.327581314062512</v>
       </c>
       <c r="G97">
-        <v>-13.43813780876808</v>
+        <v>-10.05401208434106</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.796280033533778</v>
       </c>
       <c r="E98">
-        <v>-42.96262445904696</v>
+        <v>-40.12687139307374</v>
       </c>
       <c r="F98">
-        <v>-5.291354322435882</v>
+        <v>-6.116407427256787</v>
       </c>
       <c r="G98">
-        <v>-13.97892038842634</v>
+        <v>-10.75046479161969</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.16008677824563</v>
       </c>
       <c r="E99">
-        <v>-44.42907566847684</v>
+        <v>-42.45110388479954</v>
       </c>
       <c r="F99">
-        <v>-5.391740854511543</v>
+        <v>-6.311045602422976</v>
       </c>
       <c r="G99">
-        <v>-13.88055580409075</v>
+        <v>-10.94960403744347</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.44111092132453</v>
       </c>
       <c r="E100">
-        <v>-46.08517257663695</v>
+        <v>-45.09096875062296</v>
       </c>
       <c r="F100">
-        <v>-5.32547394738979</v>
+        <v>-6.038477107103618</v>
       </c>
       <c r="G100">
-        <v>-14.12384945104455</v>
+        <v>-11.23577752549469</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.6234039015094</v>
       </c>
       <c r="E101">
-        <v>-47.99897361938856</v>
+        <v>-45.45794496301955</v>
       </c>
       <c r="F101">
-        <v>-5.733716597776666</v>
+        <v>-5.846326519248036</v>
       </c>
       <c r="G101">
-        <v>-14.57530854623497</v>
+        <v>-11.58888031271336</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.68715522934863</v>
       </c>
       <c r="E102">
-        <v>-50.20630129036935</v>
+        <v>-48.17784834269154</v>
       </c>
       <c r="F102">
-        <v>-5.794136059402056</v>
+        <v>-6.493650912696098</v>
       </c>
       <c r="G102">
-        <v>-14.79827047775934</v>
+        <v>-12.23100365714701</v>
       </c>
     </row>
   </sheetData>
